--- a/docs/APIdocs/API_메타카탈로그.xlsx
+++ b/docs/APIdocs/API_메타카탈로그.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.개요" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.엔드포인트_메타" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.공시유형_메타" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.LLM_서머리" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.자연키_인덱스" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.외래키_관계" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.검증_샘플_로그" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.종류인덱스_카드" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.다운로드_문서종류_선별" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.전체데이터_카테고리_선별" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="0.개요" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1.엔드포인트_메타" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2.공시유형_메타" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3.LLM_서머리" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4.자연키_인덱스" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5.외래키_관계" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6.검증_샘플_로그" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7.종류인덱스_카드" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8.다운로드_문서종류_선별" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9.전체데이터_카테고리_선별" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0.개요'!$A$1:$B$31</definedName>
@@ -845,7 +845,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>DART OpenAPI·공정위 OpenAPI·BOK ECOS·KOSIS·KRX 등 외부 API의 endpoint 응답 구조·자연키·LLM 서머리·노드/엣지 매핑을 단일 진실 원천(SSOT)으로 잠금. 이후 청킹·임베딩·3DB 적재 코드가 이 카탈로그를 참조하여 일관된 doc_type/anchor를 흘려보냄.</t>
+          <t>DART OpenAPI·공정위 OpenAPI·BOK ECOS·KOSIS·KRX 등 외부 API의 endpoint 응답 구조·자연키·LLM 서머리·노드/엣지 매핑을 단일 진실 원천(SSOT)으로 잠금. 이후 청킹·임베딩·3DB 적재 코드가 이 카탈로그를 참조하여 일관된 doc_type/anchor를 흘려보냄. [2026-06 갱신: 데이터 소스를 DART OpenAPI(DS001~DS005) + PDF/XBRL 단일로 확정. FTC·BOK ECOS·KOSIS·KRX·뉴스는 미사용으로 전환(코드/적재 제거). 아래 1.엔드포인트_메타 사용여부 열 참조.]</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:Q108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2365,6 +2365,11 @@
           <t>LLM 요약(미리보기)</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>사용여부(2026-06)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
@@ -2443,6 +2448,11 @@
       <c r="P2" s="17" t="inlineStr">
         <is>
           <t>2020 년부터 2025 년까지 반도체 5 대 기업 (삼성전자, SK 하이닉스, 동진쎄미켐, 솔브레인, 한미반도체) 의 공시 데이터를 검색할 수 있는 API 엔드포인트로, 공시 번호 (rcept_no) 를 기준으로 후속 분석을 수행할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -2521,6 +2531,11 @@
           <t>DS001 카테고리 '기업개황' API는 지정된 기업 코드와 인증 키를 통해 해당 회사의 기본 정보, 대표자, 주소, 상장 종목명, 사업 분야, 설립일 및 재무제표 연도 등 핵심 공시 데이터를 1 회 호출 시점에 제공합니다.</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
@@ -2593,6 +2608,11 @@
           <t>공시서류원본파일은 DART 공시시스템의 사업보고서 등 공시문서의 압축된 원본 파일(zip)을 제공하며, XBRL 형식 등의 상세 데이터를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
@@ -2665,6 +2685,11 @@
           <t>한국 기업 공시·재무 데이터 API 엔드포인트로, 고유번호 (전 기업 zip) 카테고리 (DS001) 에 속하며 crtfc_key 필수 파라미터를 통해 12MB 규모의 약 11만 개 기업의 corp_code, corp_name, stock_code, modify_date 정보를 1 회 다운로드 후 로컬 캐시로 제공하는 데이터 소스입니다.</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
@@ -2741,6 +2766,11 @@
           <t>이 데이터는 한국거래소 IRDS API(DS002)를 통해 조회할 수 있는 기업의 증자 또는 감자 현황 정보를 제공하며, 증자/감자 승인 번호, 기업 분류, 주식 종류, 발행 주식 수, 발행 주식 총액, 주식 당 액면가, 액면가 총액, 결정일 등 핵심 재무 및 주식 구조 변경 사항을 포함합니다.</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
@@ -2817,6 +2847,11 @@
           <t>배당에 관한 사항(DS002)은 기업의 배당금 지급 계획, 기준일, 액수 등 주주환원 정책과 관련된 공시 정보를 담고 있으며, 사업보고서 또는 분기보고서의 '주주총회안건' 또는 '배당안건' 섹션에 대응됩니다.</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
@@ -2893,6 +2928,11 @@
           <t>DS002 카테고리 내 '자기주식 취득 및 처분 현황' 데이터는 기업의 자기주식 취득·처분·보유량 및 관련 금액 정보를 제공하는 것으로, 분기별·연도별 재무제표 제출서에 포함된 섹션에 대응됩니다.</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -2969,6 +3009,11 @@
           <t>최대주주 현황 (hyslrSttus) 은 DS002 카테고리에서 기업의 최대주주 이름, 보유 주식 수, 지분율, 연도별 변동 내역 등을 제공하는 공시 데이터입니다.</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
@@ -3045,6 +3090,11 @@
           <t>최대주주 변동현황 (hyslrChgSttus) 은 DS002 공시 카테고리에서 기업의 최대주주 변경 사항, 변경일, 보유 주식 수, 변경 사유 등을 포함하는 공시 데이터를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
@@ -3121,6 +3171,11 @@
           <t>mrhlSttus 엔드포인트는 공시데이터 DS002 카테고리 내 소액주주현황 정보를 제공하며, 특정 기업의 연도별 소액주주 수, 총주주 수, 보유 주식 수 및 비율 등 핵심 재무 지표를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
@@ -3201,6 +3256,11 @@
           <t>DS002 카테고리 내 '임원 현황' 데이터를 제공하며, 기업 코드, 사업연도, 보고서 코드 등 필수 파라미터를 통해 임원의 성별, 출생연월, 직함, 주요 경력, 주주 관련 여부, 재직 기간 등 핵심 정보를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
@@ -3277,6 +3337,11 @@
           <t>DS002 카테고리 내 '직원 현황' 데이터는 공시된 재무제표의 부록 섹션에 포함된 기업별 직원 수, 성별 구성, 평균 근로시간, 연봉 총액 및 월급 등 인력 관리 핵심 지표를 담고 있습니다.</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
@@ -3353,6 +3418,11 @@
           <t>이 데이터는 DS002 카테고리 내 '이사·감사 전체의 보수현황'을 조회하는 API 엔드포인트로, 특정 기업과 연도별 임원 보수, 주식 보상, 기타 보상 등 재무제표 관련 상세 정보를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
@@ -3433,6 +3503,11 @@
           <t>개인별 보수지급 금액은 공시 의무 대상자에 대한 임원 및 주요 직원의 보수 지급 내역을 나타내며, DS002 카테고리 내 재무제표 관련 보고서 섹션에 해당합니다.</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
@@ -3509,6 +3584,11 @@
           <t>이 데이터는 DS002 공시 카테고리 내 '이사·감사 전체의 보수현황 (상위 5명)' 섹션에 포함된 정보로, 특정 기업의 재무제표 연도별 이사 및 감사의 보수 총액과 구성 내역을 제공합니다.</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
@@ -3589,6 +3669,11 @@
           <t>타법인 출자현황 (otrCprInvstmntSttus) 은 공시 데이터 DS002 카테고리에서 특정 기업의 해외 및 국내 타법인에 대한 투자 현황을 담고 있으며, 취득일, 투자목적, 자산규모, 지분율, 평가손익 등 핵심 재무 지표를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
@@ -3665,6 +3750,11 @@
           <t>공모자금의 사용내역 (pssrpCptalUseDtls) 은 DS002 카테고리에서 기업의 공모주식 발행으로 조달된 자금이 실제 사용된 목적, 금액, 시기 및 잔여 자금 처리 현황을 상세히 기록한 공시 데이터입니다.</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
@@ -3739,6 +3829,11 @@
       <c r="P19" s="17" t="inlineStr">
         <is>
           <t>사모자금의 사용내역 (prvsrpCptalUseDtls) 은 DS002 카테고리 내의 필수 공시 항목으로, 기업의 사모자금 사용 계획 대비 실제 사용 내역, 잔액, 발생 사유 및 사용 목적 등을 상세히 담고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -3809,6 +3904,11 @@
           <t>미상환 전환사채 발행현황 (DS002) 은 기업의 전환사채 잔여 발행 잔액, 전환가, 전환조건, 전환가능 주식종목, 예상 연도별 전환액, 전환이행 여부 및 미상환 전환사채 잔액 등 주요 재무 정보를 제공하는 공시 데이터입니다.</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
@@ -3881,6 +3981,11 @@
           <t>회사채 미상환 잔액 데이터는 DS002 카테고리에서 제공되며, 지정된 기업 코드와 사업 연도, 보고서 코드를 통해 해당 기업의 채무 잔액 정보를 반환합니다.</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
@@ -3953,6 +4058,11 @@
           <t>단기사채 미상환 잔액은 기업의 단기 부채 중 만기가 1 년 이내인 채권 잔액을 의미하며, 재무제표의 부채 항목에서 만기별 분포를 통해 기업의 단기 유동성 부담을 파악할 수 있는 데이터입니다.</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
@@ -4025,6 +4135,11 @@
           <t>기업어음증권 미상환 잔액 (cprcndNrdmpBlce) 은 DS002 재무제표 항목 중 만기별 CP 잔액 정보를 제공하며, 재무상태표의 유동부채 및 비유동부채 섹션에 해당합니다.</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
@@ -4101,6 +4216,11 @@
           <t>채무증권 발행실적 (detScritsIsuAcmslt) 은 기업의 채무증권 발행 관련 상세 정보를 담은 공시 데이터로, 발행 금액, 이자, 만기, 발행일 등 재무적 세부 사항을 포함합니다.</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
@@ -4177,6 +4297,11 @@
           <t>신종자본증권 미상환 잔액 (DS002) 은 기업의 재무제표에서 신종자본증권에 대한 미상환 금액, 만기 연도별 잔액, 그리고 특정 기간 초과 잔액 등을 상세히 기재한 항목입니다.</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
@@ -4253,6 +4378,11 @@
           <t>조건부 자본증권 미상환 잔액 (cndlCaplScritsNrdmpBlce) 은 DS002 카테고리 재무제표 항목으로, 기업의 조건부 자본증권에 대한 미상환 잔액 및 연도별 초과/미달 잔액 정보를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
@@ -4329,6 +4459,11 @@
           <t>회계감사인의 명칭 및 감사의견(DS002)은 공시된 재무제표에 대한 감사인의 공식 의견, 감사보고서 번호, 주요 감사 사항, 강조 사항 등을 포함하는 핵심 감사 정보입니다.</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
@@ -4405,6 +4540,11 @@
           <t>감사용역체결현황 (adtServcCnclsSttus) 은 DS002 카테고리 내의 필수 파라미터 (crtfc_key, corp_code, bsns_year, reprt_code) 를 통해 기업의 감사인 선정, 계약 금액, 계약일, 실제 집행 기간 및 감사인 변경 이력을 제공하는 공시 데이터입니다.</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
@@ -4481,6 +4621,11 @@
           <t>회계감사인과의 비감사용역 계약체결(DS002) 데이터는 공시된 회계감사인의 감사 외 업무 수행 계약 체결 현황을 포함하며, 계약 대상 서비스 내용, 계약 금액, 계약 기간, 체결 일자 등 핵심 정보를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
@@ -4555,6 +4700,11 @@
       <c r="P30" s="17" t="inlineStr">
         <is>
           <t>사외이사 등 외부 임원의 현황을 포함하는 공시 데이터로, 기업 코드와 사업 연도를 기반으로 해당 기업의 외부 임원 구성, 임기, 선임/해임 사유 및 날짜 등 핵심 정보를 제공합니다.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -4629,6 +4779,11 @@
           <t>기타 정기보고서 정보는 공식 공시 가이드에 정의된 30 여 개의 엔드포인트 중 하나로, 삼성전자, SK 하이닉스 등 주요 반도체 기업들의 2020 년부터 2025 년까지의 재무 및 경영 현황을 포함하는 다양한 보고서 섹션 데이터를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
@@ -4709,6 +4864,11 @@
           <t>단일회사 주요계정(DS003)은 공시된 재무제표 내 특정 계정科目的 흐름과 잔액을 상세히 보여주는 데이터이며, 보고서 섹션별 계정명, 시점, 금액, 그리고 비교 항목 정보를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
@@ -4789,6 +4949,11 @@
           <t>다중회사 주요계정(DS003) API는 삼성전자, SK하이닉스 등 반도체 5사의 재무제표에서 주요 계정과목별 흐름 (현금, 영업, 투자, 재무 등) 과 조정 항목을 년도별, 보고서별 상세 내역을 제공합니다.</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
@@ -4869,6 +5034,11 @@
           <t>fnlttSinglAcntAll API는 금융감독원 FINTT 데이터를 통해 특정 기업의 연도별 재무제표 내 계정과목별 상세 내역을 조회할 수 있는 단일회사 전체 재무제표 데이터를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
@@ -4949,6 +5119,11 @@
           <t>XBRL 택사노미는 DS003 카테고리에서 제공되며, crtfc_key 와 sj_div 파라미터를 통해 회사의 재무제표 계정 정보를 반환합니다. 이 데이터는 계정 ID, 한글/영문 명칭, IFRS 참조 정보, 데이터 타입 등을 포함하여 회사 간 재무 항목 비교 분석에 활용됩니다.</t>
         </is>
       </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
@@ -5025,6 +5200,11 @@
           <t>단일회사 주요 재무지표 (fnlttSinglIndx) 는 공시된 재무제표 내 특정 항목별 수치와 명칭을 제공하는 API로, 보고서 섹션별 상세 재무 데이터를 추출하기 위해 사용됩니다.</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
@@ -5099,6 +5279,11 @@
       <c r="P37" s="17" t="inlineStr">
         <is>
           <t>다중회사 주요 재무지표 (fnlttCmpnyIndx) 는 공시된 재무제표에서 특정 재무지표 (예: 매출액, 영업이익 등) 의 시계열 데이터를 추출하여 제공하는 API 로, 보고서 섹션별 핵심 재무성능을 분석하는 데 사용됩니다.</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -5173,6 +5358,11 @@
           <t>재무제표 원본파일 (XBRL) 은 재무제표의 각 항목별 상세 데이터와 주석을 포함하는 표준화된 XML 포맷으로, 주석 파싱을 통해 재무제표 각 섹션의 상세 설명을 추출할 수 있습니다.</t>
         </is>
       </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
@@ -5253,6 +5443,11 @@
           <t>5% 이상 대량보유자 신고 데이터를 제공하는 DS004 카테고리 API로, 기업별 누적 보유 주식 수와 비율, 신고 일자 등 핵심 재무 정보를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
@@ -5331,6 +5526,11 @@
       <c r="P40" s="17" t="inlineStr">
         <is>
           <t>임원·주요주주 소유보고 (DS004) 는 임원의 본인 주식 보유 변동 내역과 주요주주 현황을 담은 공시 데이터로, crtfc_key 와 corp_code 파라미터를 통해 특정 기업의 임원 주식 보유 현황을 조회할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -5409,6 +5609,11 @@
           <t>주식양수도결정(DS005)은 기업이 다른 회사의 주식을 양도하거나 인수하는 거래를 승인한 내용을 공시하는 API로, 공시문서 내 주식양수도결정 섹션에 해당합니다.</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="23" t="inlineStr">
@@ -5485,6 +5690,11 @@
           <t>자기주식 취득 결정(DS005)은 기업이 자체 발행 주식을 취득하는 계획과 실행 내역을 공시하는 보고서 섹션으로, 취득 목적, 기간, 가격, 보유 주식 수, 배당금 등 핵심 재무 정보를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
@@ -5559,6 +5769,11 @@
       <c r="P43" s="17" t="inlineStr">
         <is>
           <t>자기주식 처분 결정 (tsstkDpDecsn) 은 DS005 카테고리 내의 API 엔드포인트로, 지정된 기간 동안 기업이 자기주식을 매수하거나 매도한 건수, 잔량, 단가 등 상세 거래 내역을 제공합니다.</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -5633,6 +5848,11 @@
           <t>삼성전자, SK하이닉스, 동진쎄미켐, 솔브레인, 한미반도체 등 반도체 5사의 자기주식취득 신탁계약 체결 결정에 대한 공시 데이터를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="23" t="inlineStr">
@@ -5705,6 +5925,11 @@
           <t>자기주식취득 신탁계약 해지 결정은 DS005 카테고리 내 'tsstkAqTrctrCnsDecsn' 엔드포인트를 통해 제공되며, 계약 해지 사유, 기간, 당사자 정보를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="23" t="inlineStr">
@@ -5777,6 +6002,11 @@
           <t>유상증자 결정 (piicDecsn) 은 DS005 카테고리 공시 데이터로, 기업의 자본 증가 계획 및 주주총회 결정 사항을 포함하며, 발행 주식 수, 액면가, 배당금 등 재무적 핵심 정보를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="23" t="inlineStr">
@@ -5849,6 +6079,11 @@
           <t>무상증자 결정 (fricDecsn) 은 DS005 카테고리 공시 데이터로, 기업의 주식 총수 및 발행 주식 수, 주식당 평가액, 그리고 무상증자 시 증자 주식 수 등 자본구조 변경 관련 핵심 재무 지표를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="23" t="inlineStr">
@@ -5921,6 +6156,11 @@
           <t>유무상증자 결정 (pifricDecsn) 은 DS005 카테고리 내의 API 엔드포인트로, 지정된 기간 동안 기업의 유상 및 무상증자 관련 최종 결정 사항을 통합하여 제공합니다.</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
@@ -5993,6 +6233,11 @@
           <t>감자 결정(DS005)은 공시된 재무제표의 주요 계정 항목인 감자 (감가상각비) 에 대한 결정 사항으로, crstk_ostk_co(감자 잔고), fv_ps(감가상각비), cr_rt_ostk(감자 잔고 비율) 등 핵심 재무 지표를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="inlineStr">
@@ -6065,6 +6310,11 @@
           <t>채권은행 등의 관리절차 개시(DS005)는 공시대상 기업이 채권은행과 관련된 관리 절차를 시작할 때 제출하는 보고서로, 공시번호와 공시일 등 핵심 정보를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
@@ -6137,6 +6387,11 @@
           <t>상각형 조건부자본증권 발행결정(DS005)은 기업이 자본잠식 위험을 완화하기 위해 발행하는 조건부자본증권의 상각 관련 정보를 담은 공시 데이터로, 재무제표의 자본잠식 평가 및 자본충족 계획 수립 시 참조됩니다.</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="23" t="inlineStr">
@@ -6209,6 +6464,11 @@
           <t>자산양수도 (기타) 및 풋백옵션 거래에 대한 상세 정보를 제공하는 DS005 카테고리 API이며, 지정된 기업 코드와 기간 범위 내에서 해당 재무 거래 내역을 조회할 수 있습니다.</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="23" t="inlineStr">
@@ -6285,6 +6545,11 @@
           <t>타법인 주식 및 출자증권 양수결정(DS005)은 공시된 M&amp;A 거래에서 타법인에 대한 주식 또는 출자증권을 양수할지 여부를 결정하는 내용을 담고 있으며, 양수 금액, 수량, 양수 후 지분율 등 핵심 재무 정보를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="23" t="inlineStr">
@@ -6357,6 +6622,11 @@
           <t>타법인 주식 및 출자증권 양도결정 (otcprStkInvscrTrfDecsn) 은 공시 코드 DS005 카테고리 내의 필수 공시 항목으로, 지정된 기간 동안 특정 기업 (corp_code) 이 타법인에 대한 주식이나 출자증권을 양도한 사실과 양도 상세 정보를 담고 있습니다.</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="23" t="inlineStr">
@@ -6429,6 +6699,11 @@
           <t>주식교환 및 이전 결정에 대한 공시 데이터를 제공하며, 교환 비율과 대상 기업 등 핵심 정보를 포함하고 있습니다.</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="23" t="inlineStr">
@@ -6505,6 +6780,11 @@
           <t>회사분할 결정 (cmpDvDecsn) 은 DS005 카테고리 내의 API 엔드포인트로, 지정된 기간 (bgn_de~end_de) 동안 특정 기업 (corp_code) 에서 발생한 분할 비율 및 신설회사 정보를 제공하는 데이터입니다.</t>
         </is>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="23" t="inlineStr">
@@ -6577,6 +6857,11 @@
           <t>회사분할합병 결정(DS005)은 공시법상 분할 또는 합병을 결정한 사실을 공시하는 보고서 섹션으로, 필수 파라미터인 crtfc_key, corp_code, bgn_de, end_de를 통해 특정 기업과 기간의 결정 내역을 조회할 수 있습니다.</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="23" t="inlineStr">
@@ -6649,6 +6934,11 @@
           <t>회사합병 결정 (ID: othcmpMrgDecsn) 은 DS005 카테고리 내의 API 엔드포인트로, 지정된 기간 (bgn_de~end_de) 동안 특정 기업 (corp_code) 의 합병 비율과 상대방 정보를 포함합니다.</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="23" t="inlineStr">
@@ -6723,6 +7013,11 @@
       <c r="P59" s="17" t="inlineStr">
         <is>
           <t>교환사채권 발행결정 (exbdIsDecsn) 은 DS005 카테고리 내의 공시 데이터로, 기업의 교환사채권 발행 관련 결정 사항, 발행 조건, 그리고 관련 재무 지표가 포함된 보고서 섹션입니다.</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -6797,6 +7092,11 @@
           <t>신주인수권부사채권 발행결정(BW 발행)은 DS005 카테고리에서 공시된 신주인수권부사채 발행 관련 결정 사항을 포함하며, 해당 보고서 섹션은 기업의 자본 조달 계획 및 채권 발행 조건을 명시합니다.</t>
         </is>
       </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="23" t="inlineStr">
@@ -6869,6 +7169,11 @@
           <t>전환사채권 발행결정(DS005)은 기업이 전환사채(CB)를 발행하기로 결정한 사실을 공시하는 데이터로, 재무제표 주석이나 공시문서 내 자본시장법 관련 공시 섹션에 해당합니다.</t>
         </is>
       </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="23" t="inlineStr">
@@ -6941,6 +7246,11 @@
           <t>DS005 카테고리 '소송 등의 제기' 데이터는 기업의 소송 발생 여부, 결과, 청구 금액 및 관련 당사자 정보를 포함하며, 재무제표 주석 또는 공시 보고서의 소송 관련 섹션에 대응됩니다.</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="23" t="inlineStr">
@@ -7015,6 +7325,11 @@
       <c r="P63" s="17" t="inlineStr">
         <is>
           <t>영업양수 결정 (DS005) 은 기업이 특정 날짜 범위 내에서 영업양수 계약을 체결한 사실과 관련 재무제표, 양수 대가, 양수 대상 자산 및 부채의 세부 내역을 공시하는 문서입니다.</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -7089,6 +7404,11 @@
           <t>영업양도 결정 (DS005) 은 공시 데이터 중 영업양도 관련 상세 정보를 제공하는 API 엔드포인트로, 지정된 기간 내 특정 기업의 영업양도 결정 내역을 조회할 수 있습니다.</t>
         </is>
       </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="23" t="inlineStr">
@@ -7161,6 +7481,11 @@
           <t>타입 API 엔드포인트인 'tgastInhDecsn'은 유형자산 양수 결정 관련 공시 데이터를 제공하며, 필수 파라미터로 기업 코드와 기간을 입력받아 자산 양수 대상, 양수 여부, 금액 및 비율 등 핵심 재무 정보를 반환합니다.</t>
         </is>
       </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="23" t="inlineStr">
@@ -7233,6 +7558,11 @@
           <t>유형자산 양도 결정(DS005)은 기업의 유형자산 매각 또는 처분 계획을 공시하는 보고서 섹션으로, crtfc_key, corp_code, bgn_de, end_de 파라미터를 통해 특정 기간과 기업에 대한 양도 내역을 조회할 수 있습니다.</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="23" t="inlineStr">
@@ -7305,6 +7635,11 @@
           <t>영업정지(DS005) 데이터는 공시된 영업정지 사유, 일시 및 결과를 담은 보고서 섹션으로, 필수 파라미터인 crtfc_key, corp_code, bgn_de, end_de 를 통해 특정 기업의 정지 기간을 조회할 수 있습니다.</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="23" t="inlineStr">
@@ -7377,6 +7712,11 @@
           <t>부도발생(DS005)은 공시 데이터를 통해 기업의 부도 관련 정보를 추출하는 API로, crtfc_key, corp_code, bgn_de, end_de 파라미터를 입력받아 rcept_no, rcept_dt 등 핵심 필드를 반환합니다.</t>
         </is>
       </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="23" t="inlineStr">
@@ -7449,6 +7789,11 @@
           <t>회생절차 개시신청은 DS005 카테고리에서 기업의 회생절차 개시 신청 관련 정보를 제공하는 API이며, 요청 시 회생절차 번호와 개시일 등 핵심 데이터를 반환합니다.</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="23" t="inlineStr">
@@ -7521,6 +7866,11 @@
           <t>해산사유 발생(DS005)은 공시 시스템의 DS005 카테고리에서 기업의 해산 사유, 접수 번호 및 발생 일자 등 해산 관련 핵심 정보를 제공하는 API 엔드포인트입니다.</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="23" t="inlineStr">
@@ -7595,6 +7945,11 @@
       <c r="P71" s="17" t="inlineStr">
         <is>
           <t>해외증권시장 주권등 상장 결정(DS005)은 특정 기업(삼성전자, SK하이닉스 등)이 해외 증권시장에 주식을 상장하거나 상장 폐지되는 과정의 결정 사항, 상장일, 상장 주식 수, 상장 방법, 상장 종목 등을 포함하는 공시 데이터입니다.</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -7665,6 +8020,11 @@
           <t>단일판매·공급계약 체결 (DS005) 은 공시검색 API 에서 detail_ty 파라미터로 'I001'을 지정하여 조회할 수 있는 항목으로, 특정 기업 (corp_code) 의 일정 기간 (bgn_de~end_de) 동안 체결된 주요 판매 및 공급 계약 정보를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="24" t="inlineStr">
@@ -7733,6 +8093,11 @@
           <t>FTC 공시 데이터를 기반으로 전년 12월 기준 5월에 발표된 대규모기업집단 지정 현황 ( groupName, dataYear, designateDate, repreCmpyName, designateRsn) 을 제공하는 API 엔드포인트입니다.</t>
         </is>
       </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="24" t="inlineStr">
@@ -7805,6 +8170,11 @@
           <t>지정된 대규모기업집단 소속회사 조회 API 는 금융감독원 공시 데이터를 기반으로 특정 기업집단 내 비상장 및 상장 계열사의 기업명, 사업자등록번호, 법인번호, 그룹명, 계열사 여부 정보를 제공하며, 그룹과 계열사 간의 매핑 관계를 파악하는 데 활용됩니다.</t>
         </is>
       </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="24" t="inlineStr">
@@ -7877,6 +8247,11 @@
           <t>대규모기업집단 소속회사 참여업종 정보는 계열사별 KSIC 업종 분류를 제공하는 API로, FTC 카테고리에서 서비스키, 연도, 기업집단명을 필수 파라미터로 요구합니다.</t>
         </is>
       </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="24" t="inlineStr">
@@ -7949,6 +8324,11 @@
           <t>내부지분 (대동비교) API 는 삼성전자를 포함한 반도체 5사의 주요 주주별 지분율 데이터를 제공하며, FTC 카테고리 내의 내부지분 현황 보고서 섹션에 대응됩니다.</t>
         </is>
       </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="24" t="inlineStr">
@@ -8021,6 +8401,11 @@
           <t>특수관계인 내부지분 (spctlyRelPrsnInnrShrhldSttus) 은 금융감독원 공시 데이터를 기반으로 특정 기업의 동일인, 친족, 임원 및 비영리법인의 지분 보유 현황을 제공하는 API 엔드포인트로, 반도체 5사의 재무 건전성 및 지배구조 분석 시 필수적으로 참조해야 하는 FTC 카테고리 데이터입니다.</t>
         </is>
       </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="24" t="inlineStr">
@@ -8093,6 +8478,11 @@
           <t>FTC 공시 데이터를 통해 기업집단별 순환출자 구조를 파악할 수 있는 API로, 지정된 기업집단과 연도별 순환출자 고리 정보를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="24" t="inlineStr">
@@ -8165,6 +8555,11 @@
           <t>비상장 5사 계열사의 재무 상태를 나타내는 '소속회사 재무현황' API 데이터를 요약하면, 자산, 자본, 매출액, 영업이익, 당기순이익 등 핵심 재무 지표를 제공합니다.</t>
         </is>
       </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="24" t="inlineStr">
@@ -8237,6 +8632,11 @@
           <t>FTC 카테고리 소속회사 주주현황 API는 삼성전자, SK하이닉스 등 반도체 5사의 2020 년부터 2025 년까지의 소유주별 지분 현황 데이터를 제공하며, 특정 그룹의 지분율 추이와 주요 주주 변동성을 분석하는 보고서 섹션에 대응됩니다.</t>
         </is>
       </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="24" t="inlineStr">
@@ -8309,6 +8709,11 @@
           <t>소속회사 임원현황은 한국거래소(FKTS) 공시 데이터를 통해 특정 그룹의 임원 명단, 성명, 직함, 임기 등을 조회할 수 있는 API 엔드포인트이며, 반도체 기업들의 경영진 구성 변화를 분석하는 보고서 섹션에 활용됩니다.</t>
         </is>
       </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="24" t="inlineStr">
@@ -8381,6 +8786,11 @@
           <t>지주회사의 자회사 및 손자회사 구조를 파악할 수 있는 FT C(공정거래위원회) 공시 데이터를 제공하며, SK 그룹 등 대기업의 계열사 관계 분석에 활용됩니다.</t>
         </is>
       </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="24" t="inlineStr">
@@ -8453,6 +8863,11 @@
           <t>이 API 는 계열사 편입, 제외 또는 유예 상태의 시계열 변동 데이터를 제공하며, FTC(공정거래위원회) 공시 보고서의 계열회사 관계 변동 섹션에 대응합니다.</t>
         </is>
       </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="25" t="inlineStr">
@@ -8525,6 +8940,11 @@
           <t>공시서류 원본 ZIP은 공시문서 XML 파일의 첨부 파일 중 PDF 형식 데이터를 포함하는 압축 파일입니다.</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="26" t="inlineStr">
@@ -8595,6 +9015,11 @@
       <c r="P85" s="17" t="inlineStr">
         <is>
           <t>재무제표 XBRL 원본 데이터는 한국거래소 공시 시스템에서 제공하는 재무제표의 표준화된 XML 파일로, 재무제표 섹션의 모든 항목과 주석을 기계가독 가능한 형태로 담고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -8663,6 +9088,11 @@
         </is>
       </c>
       <c r="P86" s="17" t="n"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="19" t="inlineStr">
@@ -8729,6 +9159,11 @@
         </is>
       </c>
       <c r="P87" s="17" t="n"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
@@ -8795,6 +9230,11 @@
         </is>
       </c>
       <c r="P88" s="17" t="n"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="24" t="inlineStr">
@@ -8861,6 +9301,11 @@
         </is>
       </c>
       <c r="P89" s="17" t="n"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="24" t="inlineStr">
@@ -8927,6 +9372,11 @@
         </is>
       </c>
       <c r="P90" s="17" t="n"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="24" t="inlineStr">
@@ -8993,6 +9443,11 @@
         </is>
       </c>
       <c r="P91" s="17" t="n"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="39" t="inlineStr">
@@ -9035,9 +9490,6 @@
           <t>TIME, DATA_VALUE, ITEM_NAME</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>거시 — 통화정책</t>
@@ -9058,7 +9510,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="39" t="inlineStr">
@@ -9101,9 +9557,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>거시 — 단기금리</t>
@@ -9124,7 +9577,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="39" t="inlineStr">
@@ -9167,9 +9624,6 @@
           <t>TIME, DATA_VALUE, ITEM_NAME</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>거시 — 물가</t>
@@ -9190,7 +9644,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="39" t="inlineStr">
@@ -9233,9 +9691,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>거시 — 물가 (식품·에너지 제외)</t>
@@ -9256,7 +9711,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="39" t="inlineStr">
@@ -9299,9 +9758,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>거시 — 생산자물가</t>
@@ -9322,7 +9778,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="39" t="inlineStr">
@@ -9365,9 +9825,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>거시 — 경기·생산</t>
@@ -9388,7 +9845,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="39" t="inlineStr">
@@ -9431,9 +9892,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>거시 — 광공업</t>
@@ -9454,7 +9912,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="39" t="inlineStr">
@@ -9497,9 +9959,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>거시 — 환율</t>
@@ -9520,7 +9979,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="39" t="inlineStr">
@@ -9563,9 +10026,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>거시 — 고용</t>
@@ -9586,7 +10046,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="39" t="inlineStr">
@@ -9629,9 +10093,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>거시 — 수출</t>
@@ -9652,7 +10113,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="39" t="inlineStr">
@@ -9695,9 +10160,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>거시 — 수입</t>
@@ -9718,7 +10180,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="39" t="inlineStr">
@@ -9761,9 +10227,6 @@
           <t>TIME, DATA_VALUE</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>거시 — GDP</t>
@@ -9784,7 +10247,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="40" t="inlineStr">
@@ -9827,9 +10294,6 @@
           <t>PRD_DE, DT, ITM_NM</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>거시 — 인구</t>
@@ -9850,7 +10314,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="40" t="inlineStr">
@@ -9893,9 +10361,6 @@
           <t>PRD_DE, DT</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>거시 — 고용</t>
@@ -9916,7 +10381,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="40" t="inlineStr">
@@ -9959,9 +10428,6 @@
           <t>PRD_DE, DT</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>거시 — 물가 (KOSIS)</t>
@@ -9982,7 +10448,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="40" t="inlineStr">
@@ -10025,9 +10495,6 @@
           <t>PRD_DE, DT</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>거시 — 광공업 (KOSIS)</t>
@@ -10048,7 +10515,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="40" t="inlineStr">
@@ -10091,9 +10562,6 @@
           <t>PRD_DE, DT</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>거시 — 수출 (KOSIS)</t>
@@ -10114,7 +10582,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P85"/>
